--- a/etf_holdings/2026-09-15_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>-5.7%6035</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6400</v>
+        <v>6035</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.77%364,000</t>
+          <t>8.55%364,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.77%</t>
+          <t>8.55%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.24%480,000</t>
+          <t>8.28%480,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.24%</t>
+          <t>8.28%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5620</v>
+        <v>5440</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.80%323,000</t>
+          <t>6.84%323,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>6.84%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.28%1,720,000</t>
+          <t>6.37%1,720,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.28%</t>
+          <t>6.37%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>-8.76%5310</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-8.76%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5820</v>
+        <v>5310</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.70%260,000</t>
+          <t>5.37%260,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.70%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1955</v>
+        <v>1980</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.89%665,000</t>
+          <t>5.12%665,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>5.12%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.71%378,000</t>
+          <t>4.58%378,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.58%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>-4.71%972</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1020</v>
+        <v>972</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.33%1,127,000</t>
+          <t>4.26%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.27%212,000</t>
+          <t>4.22%212,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.73%529,000</t>
+          <t>3.79%529,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.63%962</t>
+          <t>-2.56%17520</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>962</v>
+        <v>17520</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.73%1,030,000</t>
+          <t>3.70%54,300</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1030000</v>
+        <v>54300</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>-7.48%890</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-7.48%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>17885</v>
+        <v>890</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.67%54,300</t>
+          <t>3.57%1,030,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>54300</v>
+        <v>1030000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-5.18%3480</t>
+          <t>+2.84%1085</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.18%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3480</v>
+        <v>1085</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.11%245,000</t>
+          <t>3.12%739,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>245000</v>
+        <v>739000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>-3.56%3255</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1055</v>
+        <v>3255</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.93%739,000</t>
+          <t>3.10%245,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>739000</v>
+        <v>245000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:37</t>
+          <t>2026-09-15 19:54:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.08%6305</t>
+          <t>-2.7%6135</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6305</v>
+        <v>6135</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.85%120,000</t>
+          <t>2.87%120,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-6.47%2025</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-6.47%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2165</v>
+        <v>2025</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.21%271,000</t>
+          <t>2.14%271,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.09%448.5</t>
+          <t>-6.07%418</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.09%</t>
+          <t>-6.07%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>448.5</v>
+        <v>418</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.01%1,200,000</t>
+          <t>1.95%1,200,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.75%11990</t>
+          <t>-2.29%11715</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.90%42,000</t>
+          <t>1.91%42,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1365</v>
+        <v>2385</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.62%306,000</t>
+          <t>1.66%179,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>306000</v>
+        <v>179000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>-2.84%1370</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2380</v>
+        <v>1370</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.60%179,000</t>
+          <t>1.63%306,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>179000</v>
+        <v>306000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-8.19%2580</t>
+          <t>+2.82%2555</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.19%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2580</v>
+        <v>2555</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.40%150,000</t>
+          <t>1.49%150,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>-1.21%1220</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1235</v>
+        <v>1220</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.31%282,000</t>
+          <t>1.34%282,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>-3.24%492.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-3.24%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2270</v>
+        <v>492.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.27%149,139</t>
+          <t>1.25%650,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>149139</v>
+        <v>650000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.59%509</t>
+          <t>-2.7%180.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>509</v>
+        <v>180.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.25%650,000</t>
+          <t>0.98%1,400,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>650000</v>
+        <v>1400000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.54%185.5</t>
+          <t>-2.81%138.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>185.5</v>
+        <v>138.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.98%1,400,000</t>
+          <t>0.96%1,778,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1400000</v>
+        <v>1778000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>-0.82%1215</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>142.5</v>
+        <v>1215</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.95%1,778,000</t>
+          <t>0.94%198,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1778000</v>
+        <v>198000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.34%1250</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1250</v>
+        <v>2315</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.91%198,000</t>
+          <t>0.89%99,139</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>198000</v>
+        <v>99139</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>+3.09%1670</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1620</v>
+        <v>1670</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.57%94,000</t>
+          <t>0.61%94,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-4.21%6600</t>
+          <t>-4.39%6310</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.21%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6600</v>
+        <v>6310</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.57%23,000</t>
+          <t>0.56%23,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:38</t>
+          <t>2026-09-15 19:54:06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.59%541</t>
+          <t>-5.18%513</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>-5.18%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>541</v>
+        <v>513</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.51%250,000</t>
+          <t>0.50%250,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.64%902</t>
+          <t>+1.56%914</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.37%110,000</t>
+          <t>0.39%110,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.96%630</t>
+          <t>-1.11%623</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.22%222</t>
+          <t>0%222</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.33%400,000</t>
+          <t>0.35%400,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-4.76%721</t>
+          <t>-0.56%705</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-4.76%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.25%95,000</t>
+          <t>0.26%95,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.48%157.5</t>
+          <t>-4.08%153</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>157.5</v>
+        <v>153</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-5.79%228</t>
+          <t>+1.1%230.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.79%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>228</v>
+        <v>230.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.57%261.5</t>
+          <t>-1.72%257</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>261.5</v>
+        <v>257</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-5.23%670</t>
+          <t>-3.2%635</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>670</v>
+        <v>635</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.96%230.5</t>
+          <t>-2.86%221</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>230.5</v>
+        <v>221</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+5.73%442.5</t>
+          <t>-2.49%431.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+5.73%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>442.5</v>
+        <v>431.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.64%3590</t>
+          <t>+2.24%685</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3590</v>
+        <v>685</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.01%5,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.59%670</t>
+          <t>-6.55%3355</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-6.55%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>670</v>
+        <v>3355</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.01%5,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>-3.27%592</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.63%1590</t>
+          <t>-4.4%1520</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1590</v>
+        <v>1520</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:39</t>
+          <t>2026-09-15 19:54:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+4.43%1415</t>
+          <t>-2.52%1355</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+4.43%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1415</v>
+        <v>1355</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">

--- a/etf_holdings/2026-09-15_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:05</t>
+          <t>2026-09-15 21:12:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:06</t>
+          <t>2026-09-15 21:13:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:07</t>
+          <t>2026-09-15 21:13:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-15_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:59</t>
+          <t>2026-09-15 22:23:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:01</t>
+          <t>2026-09-15 22:23:18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:02</t>
+          <t>2026-09-15 22:23:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-15_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:17</t>
+          <t>2026-09-15 22:29:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:18</t>
+          <t>2026-09-15 22:29:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:20</t>
+          <t>2026-09-15 22:29:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
